--- a/data/trans_bre/P05A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P05A_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 8,44</t>
+          <t>-4,96; 8,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 5,32</t>
+          <t>-9,97; 5,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 9,28</t>
+          <t>-5,24; 9,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 6,04</t>
+          <t>-3,94; 5,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 28,94</t>
+          <t>-14,4; 29,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 13,19</t>
+          <t>-20,82; 13,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 27,37</t>
+          <t>-12,47; 25,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 29,32</t>
+          <t>-14,8; 29,21</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 5,35</t>
+          <t>-8,7; 5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 9,29</t>
+          <t>-5,77; 9,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 9,09</t>
+          <t>-5,1; 9,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 13,37</t>
+          <t>1,99; 12,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 18,92</t>
+          <t>-24,02; 19,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 25,42</t>
+          <t>-13,24; 24,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 26,9</t>
+          <t>-12,66; 28,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,24; 89,32</t>
+          <t>9,47; 86,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>-3,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 17,05</t>
+          <t>-0,59; 16,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 5,49</t>
+          <t>-9,16; 6,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 8,21</t>
+          <t>-9,42; 7,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 18,06</t>
+          <t>-7,12; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 63,66</t>
+          <t>-2,18; 59,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 14,03</t>
+          <t>-20,66; 15,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 23,32</t>
+          <t>-24,93; 24,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 294,77</t>
+          <t>-31,13; 28,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,05</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>132,19%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 10,84</t>
+          <t>2,35; 10,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 4,47</t>
+          <t>-5,01; 4,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,14</t>
+          <t>-2,87; 5,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 47,49</t>
+          <t>1,33; 8,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 39,47</t>
+          <t>7,34; 38,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 11,96</t>
+          <t>-11,95; 11,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 18,1</t>
+          <t>-7,67; 16,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,01; 345,37</t>
+          <t>7,69; 58,08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-8,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 12,5</t>
+          <t>0,26; 12,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 7,76</t>
+          <t>-3,25; 7,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 7,3</t>
+          <t>-3,52; 6,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 3,2</t>
+          <t>-2,86; 5,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 43,97</t>
+          <t>0,11; 45,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 25,31</t>
+          <t>-8,89; 23,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 22,93</t>
+          <t>-9,34; 22,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 19,3</t>
+          <t>-13,39; 34,36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-13,5%</t>
+          <t>-17,22%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 14,87</t>
+          <t>4,35; 15,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 11,41</t>
+          <t>-1,52; 11,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 5,94</t>
+          <t>-6,26; 6,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 4,55</t>
+          <t>-11,5; 3,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,41; 78,34</t>
+          <t>16,22; 82,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 36,58</t>
+          <t>-3,71; 39,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 19,74</t>
+          <t>-16,04; 22,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 45,78</t>
+          <t>-45,39; 31,98</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,1</t>
+          <t>2,7; 7,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,93</t>
+          <t>-2,17; 2,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,27</t>
+          <t>-1,55; 3,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 20,91</t>
+          <t>-0,37; 3,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,98; 24,77</t>
+          <t>8,7; 24,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,62</t>
+          <t>-5,34; 6,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 9,71</t>
+          <t>-4,17; 8,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,8; 151,98</t>
+          <t>-1,87; 20,05</t>
         </is>
       </c>
     </row>
